--- a/data/trans_dic/P16A_n_R2-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P16A_n_R2-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido dos o más medicamentos en las dos últimas semanas</t>
+          <t>Población que ha consumido dos o más medicamentos en las dos últimas semanas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>30,67; 36,34</t>
+          <t>30,64; 36,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>44,91; 52,02</t>
+          <t>44,94; 51,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>38,47; 45,72</t>
+          <t>38,92; 45,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46,7; 54,94</t>
+          <t>46,57; 54,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>45,22; 50,51</t>
+          <t>44,77; 50,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,03; 64,49</t>
+          <t>59,03; 64,56</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>56,89; 63,22</t>
+          <t>56,78; 63,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>65,27; 70,56</t>
+          <t>65,2; 70,54</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>39,22; 43,47</t>
+          <t>39,54; 43,39</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>54,01; 58,22</t>
+          <t>54,31; 58,41</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>49,77; 54,67</t>
+          <t>49,94; 54,91</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>58,56; 63,25</t>
+          <t>58,35; 63,21</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,06; 10,92</t>
+          <t>7,96; 10,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,92; 18,69</t>
+          <t>14,94; 18,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15,93; 19,34</t>
+          <t>15,99; 19,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16,88; 27,07</t>
+          <t>16,05; 26,96</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,02; 20,06</t>
+          <t>16,16; 19,82</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,72; 30,24</t>
+          <t>25,78; 30,4</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,55; 28,61</t>
+          <t>24,64; 28,61</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>32,36; 56,38</t>
+          <t>32,34; 53,92</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12,41; 14,76</t>
+          <t>12,36; 14,77</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20,71; 23,43</t>
+          <t>20,67; 23,52</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20,7; 23,3</t>
+          <t>20,66; 23,25</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>26,76; 41,95</t>
+          <t>26,16; 41,44</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,72; 15,49</t>
+          <t>9,29; 15,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,07; 16,7</t>
+          <t>10,09; 16,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,34; 20,0</t>
+          <t>13,45; 20,27</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21,17; 28,0</t>
+          <t>21,25; 28,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15,93; 23,64</t>
+          <t>15,94; 23,65</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,84; 27,16</t>
+          <t>19,2; 27,68</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,06; 22,71</t>
+          <t>15,72; 22,96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>25,65; 31,91</t>
+          <t>25,6; 31,73</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13,24; 17,87</t>
+          <t>13,35; 17,95</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15,5; 20,75</t>
+          <t>15,19; 20,65</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15,65; 20,25</t>
+          <t>15,5; 20,23</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>24,51; 28,87</t>
+          <t>24,42; 29,12</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,13; 18,69</t>
+          <t>16,14; 18,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>23,69; 26,89</t>
+          <t>23,84; 26,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21,39; 24,49</t>
+          <t>21,58; 24,34</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21,46; 30,63</t>
+          <t>21,25; 30,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>28,15; 31,49</t>
+          <t>28,34; 31,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,4; 41,62</t>
+          <t>38,32; 41,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,28; 36,64</t>
+          <t>33,33; 36,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>39,16; 53,91</t>
+          <t>39,08; 53,18</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>22,7; 24,77</t>
+          <t>22,67; 24,75</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>31,65; 34,0</t>
+          <t>31,63; 33,82</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28,0; 30,28</t>
+          <t>27,98; 30,18</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>32,14; 42,13</t>
+          <t>32,18; 41,25</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido dos o más medicamentos en las dos últimas semanas</t>
+          <t>Población que ha consumido dos o más medicamentos en las dos últimas semanas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>316400; 374959</t>
+          <t>316134; 373968</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>437669; 507023</t>
+          <t>438016; 502662</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>290230; 344907</t>
+          <t>293561; 344893</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>240475; 282928</t>
+          <t>239805; 281625</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>594722; 664293</t>
+          <t>588816; 662520</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>789706; 862689</t>
+          <t>789740; 863641</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>565894; 628840</t>
+          <t>564739; 627330</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>493143; 533093</t>
+          <t>492598; 532950</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>920461; 1020276</t>
+          <t>927905; 1018300</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1249020; 1346205</t>
+          <t>1255918; 1350807</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>870547; 956131</t>
+          <t>873496; 960436</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>743994; 803526</t>
+          <t>741298; 803098</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>136565; 184963</t>
+          <t>134719; 183643</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>293121; 367101</t>
+          <t>293416; 363315</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>330725; 401559</t>
+          <t>332053; 401943</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>386634; 619896</t>
+          <t>367702; 617500</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>254317; 318451</t>
+          <t>256543; 314603</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>452065; 531480</t>
+          <t>453214; 534351</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>488206; 568844</t>
+          <t>489864; 568870</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>724188; 1261774</t>
+          <t>723733; 1206531</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>407213; 484133</t>
+          <t>405679; 484675</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>770824; 871956</t>
+          <t>769352; 875236</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>841305; 947224</t>
+          <t>839673; 944871</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1211672; 1899616</t>
+          <t>1184618; 1876661</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>53591; 85425</t>
+          <t>51207; 84645</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>48438; 80365</t>
+          <t>48553; 80953</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>72936; 109355</t>
+          <t>73558; 110837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>136888; 181082</t>
+          <t>137389; 182330</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>75900; 112608</t>
+          <t>75944; 112656</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>86416; 124543</t>
+          <t>88045; 126935</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>88174; 124723</t>
+          <t>86333; 126059</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>169430; 210766</t>
+          <t>169085; 209570</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>136046; 183690</t>
+          <t>137232; 184515</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>145710; 195005</t>
+          <t>142758; 194087</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>171582; 221947</t>
+          <t>169895; 221752</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>320307; 377320</t>
+          <t>319220; 380559</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>528509; 612482</t>
+          <t>528764; 612259</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>809982; 919467</t>
+          <t>815131; 919668</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>722350; 827273</t>
+          <t>728973; 822183</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>740790; 1057219</t>
+          <t>733530; 1048900</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>951145; 1064005</t>
+          <t>957519; 1062880</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1364796; 1479250</t>
+          <t>1361805; 1482487</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1175342; 1294202</t>
+          <t>1177354; 1293558</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1430840; 1969666</t>
+          <t>1427766; 1943108</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1510894; 1648760</t>
+          <t>1508901; 1646994</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2207496; 2371036</t>
+          <t>2205569; 2358641</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1934881; 2092409</t>
+          <t>1933488; 2085670</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2283661; 2993426</t>
+          <t>2286912; 2931131</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A_n_R2-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P16A_n_R2-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>50,6%</t>
+          <t>47,63%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>66,94%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>60,92%</t>
+          <t>58,96%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>30,64; 36,25</t>
+          <t>30,74; 36,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>44,94; 51,57</t>
+          <t>45,13; 51,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>38,92; 45,72</t>
+          <t>38,53; 45,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46,57; 54,69</t>
+          <t>43,55; 51,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>44,77; 50,38</t>
+          <t>45,28; 50,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,03; 64,56</t>
+          <t>59,08; 64,35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>56,78; 63,07</t>
+          <t>56,65; 63,09</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>65,2; 70,54</t>
+          <t>63,89; 69,43</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>39,54; 43,39</t>
+          <t>39,48; 43,38</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>54,31; 58,41</t>
+          <t>54,06; 58,4</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>49,94; 54,91</t>
+          <t>49,79; 54,7</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>58,35; 63,21</t>
+          <t>56,41; 61,17</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>30,27%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,96; 10,84</t>
+          <t>8,05; 10,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,94; 18,5</t>
+          <t>15,12; 18,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15,99; 19,36</t>
+          <t>16,1; 19,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16,05; 26,96</t>
+          <t>24,64; 28,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,16; 19,82</t>
+          <t>16,04; 19,92</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,78; 30,4</t>
+          <t>25,89; 30,44</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,64; 28,61</t>
+          <t>24,61; 28,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>32,34; 53,92</t>
+          <t>32,15; 35,87</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12,36; 14,77</t>
+          <t>12,55; 14,8</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20,67; 23,52</t>
+          <t>20,69; 23,59</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20,66; 23,25</t>
+          <t>20,63; 23,29</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>26,16; 41,44</t>
+          <t>29,05; 31,76</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>27,11%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,29; 15,35</t>
+          <t>9,68; 15,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,09; 16,82</t>
+          <t>10,04; 16,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,45; 20,27</t>
+          <t>13,58; 20,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21,25; 28,2</t>
+          <t>21,87; 28,19</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15,94; 23,65</t>
+          <t>16,32; 23,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,2; 27,68</t>
+          <t>18,82; 27,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,72; 22,96</t>
+          <t>15,96; 23,09</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>25,6; 31,73</t>
+          <t>26,67; 32,41</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13,35; 17,95</t>
+          <t>13,19; 18,01</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15,19; 20,65</t>
+          <t>15,04; 20,62</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15,5; 20,23</t>
+          <t>15,46; 20,58</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>24,42; 29,12</t>
+          <t>24,8; 29,23</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>43,32%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>35,19%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,14; 18,69</t>
+          <t>16,23; 18,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>23,84; 26,89</t>
+          <t>23,73; 26,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21,58; 24,34</t>
+          <t>21,64; 24,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21,25; 30,39</t>
+          <t>27,92; 31,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>28,34; 31,45</t>
+          <t>28,31; 31,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,32; 41,71</t>
+          <t>38,27; 41,65</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,33; 36,62</t>
+          <t>33,11; 36,53</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>39,08; 53,18</t>
+          <t>39,09; 41,86</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>22,67; 24,75</t>
+          <t>22,64; 24,8</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>31,63; 33,82</t>
+          <t>31,55; 33,96</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>27,98; 30,18</t>
+          <t>27,95; 30,08</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>32,18; 41,25</t>
+          <t>34,0; 36,23</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>260578</t>
+          <t>275528</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>513374</t>
+          <t>550270</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>773953</t>
+          <t>825798</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>316134; 373968</t>
+          <t>317125; 375827</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>438016; 502662</t>
+          <t>439814; 503196</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>293561; 344893</t>
+          <t>290673; 342654</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>239805; 281625</t>
+          <t>251927; 299650</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>588816; 662520</t>
+          <t>595529; 669451</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>789740; 863641</t>
+          <t>790416; 860854</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>564739; 627330</t>
+          <t>563474; 627521</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>492598; 532950</t>
+          <t>525187; 570757</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>927905; 1018300</t>
+          <t>926541; 1017974</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1255918; 1350807</t>
+          <t>1250190; 1350501</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>873496; 960436</t>
+          <t>870907; 956729</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>741298; 803098</t>
+          <t>790129; 856706</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>538991</t>
+          <t>590372</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>880613</t>
+          <t>742310</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1419604</t>
+          <t>1332683</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>134719; 183643</t>
+          <t>136327; 183039</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>293416; 363315</t>
+          <t>296924; 364483</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>332053; 401943</t>
+          <t>334325; 403773</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>367702; 617500</t>
+          <t>549548; 639156</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>256543; 314603</t>
+          <t>254597; 316206</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>453214; 534351</t>
+          <t>455046; 535006</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>489864; 568870</t>
+          <t>489380; 574262</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>723733; 1206531</t>
+          <t>698030; 778974</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>405679; 484675</t>
+          <t>411709; 485740</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>769352; 875236</t>
+          <t>770215; 877976</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>839673; 944871</t>
+          <t>838562; 946806</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1184618; 1876661</t>
+          <t>1278565; 1397920</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>159208</t>
+          <t>177316</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>188931</t>
+          <t>214778</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>348138</t>
+          <t>392094</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>51207; 84645</t>
+          <t>53350; 83264</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>48553; 80953</t>
+          <t>48296; 80875</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>73558; 110837</t>
+          <t>74265; 111077</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>137389; 182330</t>
+          <t>155621; 200596</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>75944; 112656</t>
+          <t>77730; 113362</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>88045; 126935</t>
+          <t>86328; 124808</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>86333; 126059</t>
+          <t>87618; 126800</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>169085; 209570</t>
+          <t>195983; 238160</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>137232; 184515</t>
+          <t>135619; 185064</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>142758; 194087</t>
+          <t>141361; 193759</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>169895; 221752</t>
+          <t>169407; 225599</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>319220; 380559</t>
+          <t>358663; 422852</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>958778</t>
+          <t>1043216</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1582918</t>
+          <t>1507359</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2541696</t>
+          <t>2550575</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>528764; 612259</t>
+          <t>531817; 613638</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>815131; 919668</t>
+          <t>811545; 917504</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>728973; 822183</t>
+          <t>731066; 824359</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>733530; 1048900</t>
+          <t>982835; 1095325</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>957519; 1062880</t>
+          <t>956577; 1067183</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1361805; 1482487</t>
+          <t>1360238; 1480349</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1177354; 1293558</t>
+          <t>1169525; 1290386</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1427766; 1943108</t>
+          <t>1457437; 1560700</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1508901; 1646994</t>
+          <t>1507175; 1650446</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2205569; 2358641</t>
+          <t>2200113; 2368078</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1933488; 2085670</t>
+          <t>1931146; 2078317</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2286912; 2931131</t>
+          <t>2464344; 2626601</t>
         </is>
       </c>
     </row>
